--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>このプロファイルはユーザは直接適用するものではなく、JP_MedicationDispenseとJP_MedicationDispenseInjectionの共通の親となる抽象プロファイルである。このプロファイルはMedicationDispenseリソースに対して、内服・外用薬剤処方調剤・払い出し記録のデータを送受信するため、JP_MedicationDispenseとJP_MedicationDispenseInjectionの各プロファイルの基礎となる制約と拡張のうち共通部分を定めている。</t>
+    <t>このプロファイルはユーザーは直接適用するものではなく、JP_MedicationDispenseとJP_MedicationDispenseInjectionの共通の親となる抽象プロファイルである。このプロファイルはMedicationDispenseリソースに対して、内服・外用薬剤処方調剤・払い出し記録のデータを送受信するため、JP_MedicationDispenseとJP_MedicationDispenseInjectionの各プロファイルの基礎となる制約と拡張のうち共通部分を定めている。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -508,7 +508,7 @@
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。処方箋全体としてのIDとしては使用しない。  
 処方箋内で同一の用法をまとめて表記されるRp番号はこのIdentifier elementの別スライスで表現する。それ以外に任意のIDを付与してもよい。  
-このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t>これは業務IDであって、リソースに対するIDではない。</t>
@@ -1161,7 +1161,7 @@
     <t>実行される調剤イベントのタイプを示す。たとえば、トライアルフィル、トライアルの完了、部分フィル、緊急フィル、サンプルなどである。</t>
   </si>
   <si>
-    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。</t>
+    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。</t>
   </si>
   <si>
     <t>実行される分配イベントのタイプを示します。たとえば、試行充填、試行の完了、部分充填、緊急充填、サンプルなど。 / Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
@@ -1310,7 +1310,7 @@
   </si>
   <si>
     <t>構造化された注釈（アノテーション）を持たないシステムの場合、作成者や時間なしで単一の注釈を簡単に伝達できる。情報を変更する可能性があるため、この要素をナラティブに含める必要がある場合がある。  
-*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。</t>
+*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザーの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。</t>
   </si>
   <si>
     <t>Event.note</t>
